--- a/backend/python/templates/TDC_Template.xlsx
+++ b/backend/python/templates/TDC_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Videos\FAAS SYSTEM\backend\python\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA49327A-5CF2-4ABD-BC3D-03DBBBD5DB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A227F895-9EE3-4E10-A45D-C6B254AA94A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09F85F88-7F48-4E0A-B303-28052CF036CC}"/>
   </bookViews>
@@ -1279,90 +1279,96 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1390,194 +1396,129 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1585,28 +1526,87 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2154,32 +2154,32 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H3" s="154" t="s">
+      <c r="H3" s="157" t="s">
         <v>53</v>
       </c>
-      <c r="I3" s="125"/>
-      <c r="J3" s="153"/>
-      <c r="K3" s="131"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="159"/>
+      <c r="K3" s="124"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="164" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="125"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="131"/>
+      <c r="B5" s="158"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -2190,154 +2190,154 @@
     </row>
     <row r="7" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
-      <c r="C7" s="150" t="s">
+      <c r="C7" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="158"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="158"/>
+      <c r="H7" s="158"/>
+      <c r="I7" s="158"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="151" t="s">
+      <c r="A8" s="172" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="125"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
+      <c r="I8" s="158"/>
+      <c r="J8" s="158"/>
+      <c r="K8" s="158"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="153"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="153"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
+      <c r="B11" s="159"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="159"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="124"/>
+      <c r="K11" s="124"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="138" t="s">
+      <c r="A12" s="175" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="125"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="158"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="158"/>
+      <c r="G12" s="158"/>
+      <c r="H12" s="158"/>
+      <c r="I12" s="158"/>
+      <c r="J12" s="158"/>
+      <c r="K12" s="158"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="153"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
+      <c r="B13" s="159"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="124"/>
+      <c r="K13" s="124"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="152" t="s">
+      <c r="A14" s="173" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="125"/>
+      <c r="B14" s="158"/>
+      <c r="C14" s="158"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="158"/>
+      <c r="F14" s="158"/>
+      <c r="G14" s="158"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="158"/>
+      <c r="J14" s="158"/>
+      <c r="K14" s="158"/>
     </row>
     <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A16" s="159" t="s">
+      <c r="A16" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="125"/>
-      <c r="C16" s="125"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="125"/>
-      <c r="G16" s="125"/>
-      <c r="H16" s="125"/>
-      <c r="I16" s="125"/>
-      <c r="J16" s="125"/>
-      <c r="K16" s="125"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="158"/>
+      <c r="K16" s="158"/>
     </row>
     <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A17" s="124" t="s">
+      <c r="A17" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="125"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="178"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
       <c r="F17" s="23"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="131"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
+      <c r="G17" s="178"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="178"/>
+      <c r="J17" s="124"/>
+      <c r="K17" s="124"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
       <c r="B18" s="24"/>
-      <c r="C18" s="148" t="s">
+      <c r="C18" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
       <c r="F18" s="24"/>
-      <c r="G18" s="148" t="s">
+      <c r="G18" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="125"/>
-      <c r="I18" s="148" t="s">
+      <c r="H18" s="158"/>
+      <c r="I18" s="160" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="125"/>
-      <c r="K18" s="125"/>
+      <c r="J18" s="158"/>
+      <c r="K18" s="158"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="124" t="s">
+      <c r="A19" s="174" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="125"/>
-      <c r="C19" s="162"/>
-      <c r="D19" s="163"/>
-      <c r="E19" s="163"/>
+      <c r="B19" s="158"/>
+      <c r="C19" s="168"/>
+      <c r="D19" s="169"/>
+      <c r="E19" s="169"/>
       <c r="F19" s="22"/>
       <c r="G19" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="164"/>
-      <c r="I19" s="164"/>
+      <c r="H19" s="170"/>
+      <c r="I19" s="170"/>
       <c r="J19" s="24" t="s">
         <v>31</v>
       </c>
@@ -2364,95 +2364,95 @@
       <c r="A21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="160"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="131"/>
+      <c r="B21" s="166"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="124"/>
       <c r="H21" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="160"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
+      <c r="I21" s="166"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="124"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="161"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="142"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="142"/>
-      <c r="G22" s="142"/>
+      <c r="B22" s="167"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
       <c r="H22" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="161"/>
-      <c r="J22" s="142"/>
-      <c r="K22" s="142"/>
+      <c r="I22" s="167"/>
+      <c r="J22" s="129"/>
+      <c r="K22" s="129"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="149" t="s">
+      <c r="A23" s="181" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="158"/>
+      <c r="D23" s="158"/>
+      <c r="E23" s="158"/>
+      <c r="F23" s="158"/>
+      <c r="G23" s="158"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="158"/>
+      <c r="K23" s="158"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="155"/>
-      <c r="B24" s="131"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="131"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="131"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="131"/>
-      <c r="J24" s="131"/>
-      <c r="K24" s="131"/>
+      <c r="A24" s="161"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="124"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="124"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="124"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="174" t="s">
+      <c r="A25" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="175"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="175"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="175"/>
-      <c r="I25" s="175"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="175"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="127"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="147" t="s">
+      <c r="A26" s="156" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="142"/>
-      <c r="C26" s="123"/>
+      <c r="B26" s="129"/>
+      <c r="C26" s="130"/>
       <c r="D26" s="29"/>
-      <c r="E26" s="146" t="s">
+      <c r="E26" s="180" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="142"/>
-      <c r="G26" s="142"/>
-      <c r="H26" s="142"/>
-      <c r="I26" s="142"/>
-      <c r="J26" s="142"/>
-      <c r="K26" s="142"/>
+      <c r="F26" s="129"/>
+      <c r="G26" s="129"/>
+      <c r="H26" s="129"/>
+      <c r="I26" s="129"/>
+      <c r="J26" s="129"/>
+      <c r="K26" s="129"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
@@ -2465,10 +2465,10 @@
         <v>8</v>
       </c>
       <c r="D27" s="57"/>
-      <c r="E27" s="179" t="s">
+      <c r="E27" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="123"/>
+      <c r="F27" s="130"/>
       <c r="G27" s="58" t="s">
         <v>7</v>
       </c>
@@ -2478,18 +2478,18 @@
       <c r="I27" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J27" s="144" t="s">
+      <c r="J27" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="123"/>
+      <c r="K27" s="130"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="31"/>
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
       <c r="D28" s="29"/>
-      <c r="E28" s="180"/>
-      <c r="F28" s="181"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="137"/>
       <c r="G28" s="107"/>
       <c r="H28" s="59"/>
       <c r="I28" s="90" t="str">
@@ -2509,19 +2509,19 @@
 )</f>
         <v/>
       </c>
-      <c r="J28" s="167" t="str">
+      <c r="J28" s="133" t="str">
         <f>IFERROR(IF(MROUND(G28*I28,10)=0, "", MROUND(G28*I28,10)), "")</f>
         <v/>
       </c>
-      <c r="K28" s="168"/>
+      <c r="K28" s="134"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="34"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
       <c r="D29" s="29"/>
-      <c r="E29" s="182"/>
-      <c r="F29" s="183"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="139"/>
       <c r="G29" s="108"/>
       <c r="H29" s="60"/>
       <c r="I29" s="90" t="str">
@@ -2541,19 +2541,19 @@
 )</f>
         <v/>
       </c>
-      <c r="J29" s="167" t="str">
+      <c r="J29" s="133" t="str">
         <f t="shared" ref="J29:J31" si="0">IFERROR(IF(MROUND(G29*I29,10)=0, "", MROUND(G29*I29,10)), "")</f>
         <v/>
       </c>
-      <c r="K29" s="168"/>
+      <c r="K29" s="134"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="31"/>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="29"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="185"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="141"/>
       <c r="G30" s="109"/>
       <c r="H30" s="91"/>
       <c r="I30" s="90" t="str">
@@ -2573,35 +2573,35 @@
 )</f>
         <v/>
       </c>
-      <c r="J30" s="167" t="str">
+      <c r="J30" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K30" s="168"/>
+      <c r="K30" s="134"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="31"/>
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="29"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="123"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="130"/>
       <c r="G31" s="110"/>
       <c r="H31" s="33"/>
       <c r="I31" s="90"/>
-      <c r="J31" s="167" t="str">
+      <c r="J31" s="133" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K31" s="168"/>
+      <c r="K31" s="134"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="31"/>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
       <c r="D32" s="29"/>
-      <c r="E32" s="145"/>
-      <c r="F32" s="123"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="130"/>
       <c r="G32" s="110"/>
       <c r="H32" s="33" t="s">
         <v>18</v>
@@ -2623,19 +2623,19 @@
 )</f>
         <v/>
       </c>
-      <c r="J32" s="169" t="str">
+      <c r="J32" s="150" t="str">
         <f t="shared" ref="J32:J34" si="1">IFERROR(MROUND(G32*I32,10),"")</f>
         <v/>
       </c>
-      <c r="K32" s="123"/>
+      <c r="K32" s="130"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="31"/>
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="29"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="123"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="130"/>
       <c r="G33" s="110"/>
       <c r="H33" s="33" t="s">
         <v>18</v>
@@ -2657,19 +2657,19 @@
 )</f>
         <v/>
       </c>
-      <c r="J33" s="169" t="str">
+      <c r="J33" s="150" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="123"/>
+      <c r="K33" s="130"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="31"/>
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="29"/>
-      <c r="E34" s="145"/>
-      <c r="F34" s="123"/>
+      <c r="E34" s="142"/>
+      <c r="F34" s="130"/>
       <c r="G34" s="106"/>
       <c r="H34" s="33" t="s">
         <v>18</v>
@@ -2691,29 +2691,26 @@
 )</f>
         <v/>
       </c>
-      <c r="J34" s="169" t="str">
+      <c r="J34" s="150" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="123"/>
+      <c r="K34" s="130"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="31"/>
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
       <c r="D35" s="29"/>
-      <c r="E35" s="141" t="s">
+      <c r="E35" s="153" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="123"/>
+      <c r="F35" s="130"/>
       <c r="G35" s="32"/>
       <c r="H35" s="33"/>
       <c r="I35" s="33"/>
-      <c r="J35" s="139" t="str">
-        <f>IF(SUM(J28:K34)=0, "", MROUND(SUM(J28:K34), 10))</f>
-        <v/>
-      </c>
-      <c r="K35" s="140"/>
+      <c r="J35" s="176"/>
+      <c r="K35" s="177"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
@@ -2724,73 +2721,73 @@
         <v>13</v>
       </c>
       <c r="D36" s="29"/>
-      <c r="E36" s="141" t="s">
+      <c r="E36" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="142"/>
-      <c r="G36" s="142"/>
-      <c r="H36" s="142"/>
-      <c r="I36" s="123"/>
-      <c r="J36" s="170"/>
-      <c r="K36" s="171"/>
+      <c r="F36" s="129"/>
+      <c r="G36" s="129"/>
+      <c r="H36" s="129"/>
+      <c r="I36" s="130"/>
+      <c r="J36" s="151"/>
+      <c r="K36" s="152"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="124" t="s">
+      <c r="A37" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="125"/>
-      <c r="C37" s="125"/>
-      <c r="D37" s="125"/>
-      <c r="E37" s="125"/>
-      <c r="F37" s="125"/>
-      <c r="G37" s="125"/>
-      <c r="H37" s="125"/>
-      <c r="I37" s="125"/>
-      <c r="J37" s="125"/>
-      <c r="K37" s="125"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="158"/>
+      <c r="D37" s="158"/>
+      <c r="E37" s="158"/>
+      <c r="F37" s="158"/>
+      <c r="G37" s="158"/>
+      <c r="H37" s="158"/>
+      <c r="I37" s="158"/>
+      <c r="J37" s="158"/>
+      <c r="K37" s="158"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="126" t="s">
+      <c r="A38" s="183" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="125"/>
-      <c r="C38" s="125"/>
-      <c r="D38" s="125"/>
-      <c r="E38" s="125"/>
-      <c r="F38" s="125"/>
-      <c r="G38" s="125"/>
-      <c r="H38" s="125"/>
-      <c r="I38" s="125"/>
-      <c r="J38" s="125"/>
-      <c r="K38" s="125"/>
+      <c r="B38" s="158"/>
+      <c r="C38" s="158"/>
+      <c r="D38" s="158"/>
+      <c r="E38" s="158"/>
+      <c r="F38" s="158"/>
+      <c r="G38" s="158"/>
+      <c r="H38" s="158"/>
+      <c r="I38" s="158"/>
+      <c r="J38" s="158"/>
+      <c r="K38" s="158"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="147" t="s">
+      <c r="A39" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="142"/>
-      <c r="C39" s="123"/>
+      <c r="B39" s="129"/>
+      <c r="C39" s="130"/>
       <c r="D39" s="39"/>
       <c r="E39" s="34" t="s">
         <v>58</v>
       </c>
       <c r="F39" s="61"/>
       <c r="G39" s="62"/>
-      <c r="H39" s="176" t="s">
+      <c r="H39" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="142"/>
-      <c r="J39" s="142"/>
-      <c r="K39" s="123"/>
+      <c r="I39" s="129"/>
+      <c r="J39" s="129"/>
+      <c r="K39" s="130"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="165" t="s">
+      <c r="A40" s="189" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="165" t="s">
+      <c r="B40" s="189" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="189" t="s">
+      <c r="C40" s="147" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="29"/>
@@ -2799,33 +2796,33 @@
       </c>
       <c r="F40" s="41"/>
       <c r="G40" s="42"/>
-      <c r="H40" s="136" t="s">
+      <c r="H40" s="155" t="s">
         <v>108</v>
       </c>
-      <c r="I40" s="136" t="s">
+      <c r="I40" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="J40" s="136" t="s">
+      <c r="J40" s="155" t="s">
         <v>109</v>
       </c>
-      <c r="K40" s="136" t="s">
+      <c r="K40" s="155" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="137"/>
-      <c r="B41" s="137"/>
-      <c r="C41" s="137"/>
+      <c r="A41" s="148"/>
+      <c r="B41" s="148"/>
+      <c r="C41" s="148"/>
       <c r="D41" s="29"/>
       <c r="E41" s="41" t="s">
         <v>37</v>
       </c>
       <c r="F41" s="41"/>
       <c r="G41" s="63"/>
-      <c r="H41" s="137"/>
-      <c r="I41" s="137"/>
-      <c r="J41" s="128"/>
-      <c r="K41" s="137"/>
+      <c r="H41" s="148"/>
+      <c r="I41" s="148"/>
+      <c r="J41" s="185"/>
+      <c r="K41" s="148"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="43"/>
@@ -3045,11 +3042,11 @@
       <c r="B45" s="50"/>
       <c r="C45" s="50"/>
       <c r="D45" s="29"/>
-      <c r="E45" s="133" t="s">
+      <c r="E45" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="F45" s="125"/>
-      <c r="G45" s="134"/>
+      <c r="F45" s="158"/>
+      <c r="G45" s="188"/>
       <c r="H45" s="51"/>
       <c r="I45" s="35"/>
       <c r="J45" s="64" t="str" cm="1">
@@ -3195,9 +3192,9 @@
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
       <c r="D51" s="12"/>
-      <c r="E51" s="130"/>
-      <c r="F51" s="131"/>
-      <c r="G51" s="129"/>
+      <c r="E51" s="123"/>
+      <c r="F51" s="124"/>
+      <c r="G51" s="125"/>
       <c r="H51" s="17"/>
       <c r="I51" s="17"/>
       <c r="J51" s="18"/>
@@ -3237,58 +3234,58 @@
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="135"/>
-      <c r="I53" s="142"/>
-      <c r="J53" s="123"/>
+      <c r="H53" s="190"/>
+      <c r="I53" s="129"/>
+      <c r="J53" s="130"/>
       <c r="K53" s="93" t="str">
         <f>IF(SUM(K42:K51)=0, "", MROUND(SUM(K42:K51), 10))</f>
         <v/>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="186"/>
-      <c r="B54" s="142"/>
-      <c r="C54" s="142"/>
-      <c r="D54" s="142"/>
-      <c r="E54" s="142"/>
-      <c r="F54" s="142"/>
-      <c r="G54" s="142"/>
-      <c r="H54" s="142"/>
-      <c r="I54" s="142"/>
-      <c r="J54" s="142"/>
-      <c r="K54" s="142"/>
+      <c r="A54" s="144"/>
+      <c r="B54" s="129"/>
+      <c r="C54" s="129"/>
+      <c r="D54" s="129"/>
+      <c r="E54" s="129"/>
+      <c r="F54" s="129"/>
+      <c r="G54" s="129"/>
+      <c r="H54" s="129"/>
+      <c r="I54" s="129"/>
+      <c r="J54" s="129"/>
+      <c r="K54" s="129"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+      <c r="A55" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="131"/>
-      <c r="C55" s="131"/>
-      <c r="D55" s="131"/>
-      <c r="E55" s="131"/>
-      <c r="F55" s="131"/>
-      <c r="G55" s="131"/>
-      <c r="H55" s="131"/>
-      <c r="I55" s="131"/>
-      <c r="J55" s="131"/>
-      <c r="K55" s="131"/>
+      <c r="B55" s="124"/>
+      <c r="C55" s="124"/>
+      <c r="D55" s="124"/>
+      <c r="E55" s="124"/>
+      <c r="F55" s="124"/>
+      <c r="G55" s="124"/>
+      <c r="H55" s="124"/>
+      <c r="I55" s="124"/>
+      <c r="J55" s="124"/>
+      <c r="K55" s="124"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="177" t="s">
+      <c r="A56" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="B56" s="142"/>
-      <c r="C56" s="123"/>
+      <c r="B56" s="129"/>
+      <c r="C56" s="130"/>
       <c r="D56" s="66"/>
-      <c r="E56" s="178" t="s">
+      <c r="E56" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="142"/>
-      <c r="G56" s="142"/>
-      <c r="H56" s="142"/>
-      <c r="I56" s="142"/>
-      <c r="J56" s="142"/>
-      <c r="K56" s="142"/>
+      <c r="F56" s="129"/>
+      <c r="G56" s="129"/>
+      <c r="H56" s="129"/>
+      <c r="I56" s="129"/>
+      <c r="J56" s="129"/>
+      <c r="K56" s="129"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
@@ -3314,31 +3311,31 @@
       <c r="I57" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J57" s="187" t="s">
+      <c r="J57" s="145" t="s">
         <v>19</v>
       </c>
-      <c r="K57" s="188"/>
+      <c r="K57" s="146"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="13"/>
       <c r="B58" s="19"/>
       <c r="C58" s="13"/>
       <c r="D58" s="20"/>
-      <c r="E58" s="247"/>
-      <c r="F58" s="181"/>
+      <c r="E58" s="143"/>
+      <c r="F58" s="137"/>
       <c r="G58" s="69"/>
       <c r="H58" s="70"/>
       <c r="I58" s="70"/>
-      <c r="J58" s="127"/>
-      <c r="K58" s="123"/>
+      <c r="J58" s="184"/>
+      <c r="K58" s="130"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="13"/>
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
       <c r="D59" s="20"/>
-      <c r="E59" s="247"/>
-      <c r="F59" s="185"/>
+      <c r="E59" s="143"/>
+      <c r="F59" s="141"/>
       <c r="G59" s="21" t="s">
         <v>18</v>
       </c>
@@ -3346,16 +3343,16 @@
       <c r="I59" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J59" s="128"/>
-      <c r="K59" s="129"/>
+      <c r="J59" s="185"/>
+      <c r="K59" s="125"/>
     </row>
     <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13"/>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
       <c r="D60" s="20"/>
-      <c r="E60" s="247"/>
-      <c r="F60" s="247"/>
+      <c r="E60" s="143"/>
+      <c r="F60" s="143"/>
       <c r="G60" s="21" t="s">
         <v>18</v>
       </c>
@@ -3365,8 +3362,8 @@
       <c r="I60" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J60" s="166"/>
-      <c r="K60" s="123"/>
+      <c r="J60" s="149"/>
+      <c r="K60" s="130"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
@@ -3377,10 +3374,10 @@
         <v>13</v>
       </c>
       <c r="D61" s="20"/>
-      <c r="E61" s="132" t="s">
+      <c r="E61" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="F61" s="123"/>
+      <c r="F61" s="130"/>
       <c r="G61" s="68"/>
       <c r="H61" s="21" t="s">
         <v>18</v>
@@ -3388,24 +3385,24 @@
       <c r="I61" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J61" s="122">
+      <c r="J61" s="182">
         <f>SUM(J58:K60)</f>
         <v>0</v>
       </c>
-      <c r="K61" s="123"/>
+      <c r="K61" s="130"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="130"/>
-      <c r="B62" s="131"/>
-      <c r="C62" s="131"/>
-      <c r="D62" s="131"/>
-      <c r="E62" s="131"/>
-      <c r="F62" s="131"/>
-      <c r="G62" s="131"/>
-      <c r="H62" s="131"/>
-      <c r="I62" s="131"/>
-      <c r="J62" s="131"/>
-      <c r="K62" s="129"/>
+      <c r="A62" s="123"/>
+      <c r="B62" s="124"/>
+      <c r="C62" s="124"/>
+      <c r="D62" s="124"/>
+      <c r="E62" s="124"/>
+      <c r="F62" s="124"/>
+      <c r="G62" s="124"/>
+      <c r="H62" s="124"/>
+      <c r="I62" s="124"/>
+      <c r="J62" s="124"/>
+      <c r="K62" s="125"/>
     </row>
     <row r="63" spans="1:11" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="67"/>
@@ -3421,43 +3418,109 @@
       <c r="A64" s="94" t="s">
         <v>110</v>
       </c>
-      <c r="B64" s="173"/>
-      <c r="C64" s="173"/>
-      <c r="D64" s="173"/>
-      <c r="E64" s="173"/>
-      <c r="F64" s="173"/>
-      <c r="G64" s="173"/>
-      <c r="H64" s="173"/>
-      <c r="I64" s="173"/>
-      <c r="J64" s="173"/>
-      <c r="K64" s="173"/>
+      <c r="B64" s="122"/>
+      <c r="C64" s="122"/>
+      <c r="D64" s="122"/>
+      <c r="E64" s="122"/>
+      <c r="F64" s="122"/>
+      <c r="G64" s="122"/>
+      <c r="H64" s="122"/>
+      <c r="I64" s="122"/>
+      <c r="J64" s="122"/>
+      <c r="K64" s="122"/>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B65" s="173"/>
-      <c r="C65" s="173"/>
-      <c r="D65" s="173"/>
-      <c r="E65" s="173"/>
-      <c r="F65" s="173"/>
-      <c r="G65" s="173"/>
-      <c r="H65" s="173"/>
-      <c r="I65" s="173"/>
-      <c r="J65" s="173"/>
-      <c r="K65" s="173"/>
+      <c r="B65" s="122"/>
+      <c r="C65" s="122"/>
+      <c r="D65" s="122"/>
+      <c r="E65" s="122"/>
+      <c r="F65" s="122"/>
+      <c r="G65" s="122"/>
+      <c r="H65" s="122"/>
+      <c r="I65" s="122"/>
+      <c r="J65" s="122"/>
+      <c r="K65" s="122"/>
     </row>
     <row r="66" spans="2:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="173"/>
-      <c r="C66" s="173"/>
-      <c r="D66" s="173"/>
-      <c r="E66" s="173"/>
-      <c r="F66" s="173"/>
-      <c r="G66" s="173"/>
-      <c r="H66" s="173"/>
-      <c r="I66" s="173"/>
-      <c r="J66" s="173"/>
-      <c r="K66" s="173"/>
+      <c r="B66" s="122"/>
+      <c r="C66" s="122"/>
+      <c r="D66" s="122"/>
+      <c r="E66" s="122"/>
+      <c r="F66" s="122"/>
+      <c r="G66" s="122"/>
+      <c r="H66" s="122"/>
+      <c r="I66" s="122"/>
+      <c r="J66" s="122"/>
+      <c r="K66" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="E36:I36"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E26:K26"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="B64:K66"/>
     <mergeCell ref="A62:K62"/>
     <mergeCell ref="A25:K25"/>
@@ -3474,72 +3537,6 @@
     <mergeCell ref="A54:K54"/>
     <mergeCell ref="J57:K57"/>
     <mergeCell ref="C40:C41"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="E36:I36"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E26:K26"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="H53:J53"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3569,62 +3566,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
-      <c r="E1" s="240"/>
-      <c r="F1" s="240"/>
-      <c r="G1" s="240"/>
-      <c r="H1" s="240"/>
-      <c r="I1" s="240"/>
-      <c r="J1" s="240"/>
-      <c r="K1" s="240"/>
+      <c r="B1" s="213"/>
+      <c r="C1" s="213"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="221" t="s">
+      <c r="A2" s="214" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="221"/>
-      <c r="C2" s="221"/>
-      <c r="D2" s="221"/>
-      <c r="E2" s="221"/>
-      <c r="F2" s="221"/>
-      <c r="G2" s="221"/>
-      <c r="H2" s="221"/>
-      <c r="I2" s="221"/>
-      <c r="J2" s="221"/>
-      <c r="K2" s="221"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="214"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="214"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="223" t="s">
+      <c r="A3" s="194" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="224"/>
-      <c r="C3" s="224"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="230" t="s">
+      <c r="B3" s="195"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="200" t="s">
         <v>107</v>
       </c>
       <c r="F3" s="116"/>
-      <c r="G3" s="241" t="s">
+      <c r="G3" s="202" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="242"/>
-      <c r="I3" s="242"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="232" t="s">
+      <c r="H3" s="203"/>
+      <c r="I3" s="203"/>
+      <c r="J3" s="204"/>
+      <c r="K3" s="205" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="226"/>
-      <c r="B4" s="199"/>
-      <c r="C4" s="199"/>
-      <c r="D4" s="227"/>
-      <c r="E4" s="231"/>
+      <c r="A4" s="197"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="201"/>
       <c r="F4" s="31"/>
       <c r="G4" s="117" t="s">
         <v>65</v>
@@ -3638,13 +3635,13 @@
       <c r="J4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="233"/>
+      <c r="K4" s="206"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="236"/>
-      <c r="B5" s="237"/>
-      <c r="C5" s="237"/>
-      <c r="D5" s="238"/>
+      <c r="A5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="217"/>
       <c r="E5" s="31"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
@@ -3656,10 +3653,10 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="214"/>
-      <c r="B6" s="215"/>
-      <c r="C6" s="215"/>
-      <c r="D6" s="216"/>
+      <c r="A6" s="207"/>
+      <c r="B6" s="208"/>
+      <c r="C6" s="208"/>
+      <c r="D6" s="209"/>
       <c r="E6" s="74"/>
       <c r="F6" s="74"/>
       <c r="G6" s="74"/>
@@ -3669,10 +3666,10 @@
       <c r="K6" s="73"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="214"/>
-      <c r="B7" s="215"/>
-      <c r="C7" s="215"/>
-      <c r="D7" s="216"/>
+      <c r="A7" s="207"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="208"/>
+      <c r="D7" s="209"/>
       <c r="E7" s="74"/>
       <c r="F7" s="74"/>
       <c r="G7" s="74"/>
@@ -3682,64 +3679,64 @@
       <c r="K7" s="73"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="220" t="s">
+      <c r="A8" s="211" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="220"/>
-      <c r="C8" s="220"/>
-      <c r="D8" s="220"/>
-      <c r="E8" s="220"/>
-      <c r="F8" s="220"/>
-      <c r="G8" s="220"/>
-      <c r="H8" s="220"/>
-      <c r="I8" s="220"/>
-      <c r="J8" s="220"/>
+      <c r="B8" s="211"/>
+      <c r="C8" s="211"/>
+      <c r="D8" s="211"/>
+      <c r="E8" s="211"/>
+      <c r="F8" s="211"/>
+      <c r="G8" s="211"/>
+      <c r="H8" s="211"/>
+      <c r="I8" s="211"/>
+      <c r="J8" s="211"/>
       <c r="K8" s="76" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="239" t="s">
+      <c r="A9" s="218" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="239"/>
-      <c r="C9" s="239"/>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
+      <c r="B9" s="218"/>
+      <c r="C9" s="218"/>
+      <c r="D9" s="218"/>
+      <c r="E9" s="218"/>
+      <c r="F9" s="218"/>
+      <c r="G9" s="218"/>
+      <c r="H9" s="218"/>
+      <c r="I9" s="218"/>
+      <c r="J9" s="218"/>
+      <c r="K9" s="218"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="223" t="s">
+      <c r="A10" s="194" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="224"/>
-      <c r="C10" s="224"/>
-      <c r="D10" s="225"/>
-      <c r="E10" s="230" t="s">
+      <c r="B10" s="195"/>
+      <c r="C10" s="195"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="200" t="s">
         <v>107</v>
       </c>
       <c r="F10" s="116"/>
-      <c r="G10" s="241" t="s">
+      <c r="G10" s="202" t="s">
         <v>64</v>
       </c>
-      <c r="H10" s="242"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="243"/>
-      <c r="K10" s="232" t="s">
+      <c r="H10" s="203"/>
+      <c r="I10" s="203"/>
+      <c r="J10" s="204"/>
+      <c r="K10" s="205" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="226"/>
-      <c r="B11" s="199"/>
-      <c r="C11" s="199"/>
-      <c r="D11" s="227"/>
-      <c r="E11" s="231"/>
+      <c r="A11" s="197"/>
+      <c r="B11" s="198"/>
+      <c r="C11" s="198"/>
+      <c r="D11" s="199"/>
+      <c r="E11" s="201"/>
       <c r="F11" s="31"/>
       <c r="G11" s="117" t="s">
         <v>65</v>
@@ -3753,13 +3750,13 @@
       <c r="J11" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="233"/>
+      <c r="K11" s="206"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="214"/>
-      <c r="B12" s="215"/>
-      <c r="C12" s="215"/>
-      <c r="D12" s="216"/>
+      <c r="A12" s="207"/>
+      <c r="B12" s="208"/>
+      <c r="C12" s="208"/>
+      <c r="D12" s="209"/>
       <c r="E12" s="74"/>
       <c r="F12" s="74"/>
       <c r="G12" s="74"/>
@@ -3771,10 +3768,10 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="214"/>
-      <c r="B13" s="215"/>
-      <c r="C13" s="215"/>
-      <c r="D13" s="216"/>
+      <c r="A13" s="207"/>
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="209"/>
       <c r="E13" s="74"/>
       <c r="F13" s="74"/>
       <c r="G13" s="74"/>
@@ -3784,10 +3781,10 @@
       <c r="K13" s="73"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="214"/>
-      <c r="B14" s="215"/>
-      <c r="C14" s="215"/>
-      <c r="D14" s="216"/>
+      <c r="A14" s="207"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="209"/>
       <c r="E14" s="74"/>
       <c r="F14" s="74"/>
       <c r="G14" s="74"/>
@@ -3797,18 +3794,18 @@
       <c r="K14" s="73"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="220" t="s">
+      <c r="A15" s="211" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="220"/>
-      <c r="C15" s="220"/>
-      <c r="D15" s="220"/>
-      <c r="E15" s="220"/>
-      <c r="F15" s="220"/>
-      <c r="G15" s="220"/>
-      <c r="H15" s="220"/>
-      <c r="I15" s="220"/>
-      <c r="J15" s="220"/>
+      <c r="B15" s="211"/>
+      <c r="C15" s="211"/>
+      <c r="D15" s="211"/>
+      <c r="E15" s="211"/>
+      <c r="F15" s="211"/>
+      <c r="G15" s="211"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="211"/>
+      <c r="J15" s="211"/>
       <c r="K15" s="84" t="s">
         <v>13</v>
       </c>
@@ -3827,234 +3824,234 @@
       <c r="K16" s="24"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="246" t="s">
+      <c r="A17" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="246"/>
-      <c r="C17" s="246"/>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="246"/>
-      <c r="K17" s="246"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="212"/>
+      <c r="E17" s="212"/>
+      <c r="F17" s="212"/>
+      <c r="G17" s="212"/>
+      <c r="H17" s="212"/>
+      <c r="I17" s="212"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="212"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="221" t="s">
+      <c r="A18" s="214" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="221"/>
-      <c r="C18" s="221"/>
-      <c r="D18" s="221"/>
-      <c r="E18" s="221"/>
-      <c r="F18" s="221"/>
-      <c r="G18" s="221"/>
-      <c r="H18" s="221"/>
-      <c r="I18" s="221"/>
-      <c r="J18" s="221"/>
-      <c r="K18" s="221"/>
+      <c r="B18" s="214"/>
+      <c r="C18" s="214"/>
+      <c r="D18" s="214"/>
+      <c r="E18" s="214"/>
+      <c r="F18" s="214"/>
+      <c r="G18" s="214"/>
+      <c r="H18" s="214"/>
+      <c r="I18" s="214"/>
+      <c r="J18" s="214"/>
+      <c r="K18" s="214"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="223" t="s">
+      <c r="A19" s="194" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="224"/>
-      <c r="C19" s="224"/>
-      <c r="D19" s="225"/>
-      <c r="E19" s="228" t="s">
+      <c r="B19" s="195"/>
+      <c r="C19" s="195"/>
+      <c r="D19" s="196"/>
+      <c r="E19" s="219" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="224"/>
-      <c r="G19" s="225"/>
-      <c r="H19" s="230" t="s">
+      <c r="F19" s="195"/>
+      <c r="G19" s="196"/>
+      <c r="H19" s="200" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="228" t="s">
+      <c r="I19" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="J19" s="225"/>
-      <c r="K19" s="232" t="s">
+      <c r="J19" s="196"/>
+      <c r="K19" s="205" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="226"/>
-      <c r="B20" s="199"/>
-      <c r="C20" s="199"/>
-      <c r="D20" s="227"/>
-      <c r="E20" s="229"/>
-      <c r="F20" s="199"/>
-      <c r="G20" s="227"/>
-      <c r="H20" s="231"/>
-      <c r="I20" s="229"/>
-      <c r="J20" s="227"/>
-      <c r="K20" s="233"/>
+      <c r="A20" s="197"/>
+      <c r="B20" s="198"/>
+      <c r="C20" s="198"/>
+      <c r="D20" s="199"/>
+      <c r="E20" s="220"/>
+      <c r="F20" s="198"/>
+      <c r="G20" s="199"/>
+      <c r="H20" s="201"/>
+      <c r="I20" s="220"/>
+      <c r="J20" s="199"/>
+      <c r="K20" s="206"/>
     </row>
     <row r="21" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="214"/>
-      <c r="B21" s="215"/>
-      <c r="C21" s="215"/>
-      <c r="D21" s="216"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="207"/>
-      <c r="G21" s="145"/>
+      <c r="A21" s="207"/>
+      <c r="B21" s="208"/>
+      <c r="C21" s="208"/>
+      <c r="D21" s="209"/>
+      <c r="E21" s="180"/>
+      <c r="F21" s="210"/>
+      <c r="G21" s="142"/>
       <c r="H21" s="31"/>
-      <c r="I21" s="146"/>
-      <c r="J21" s="145"/>
+      <c r="I21" s="180"/>
+      <c r="J21" s="142"/>
       <c r="K21" s="83" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="214"/>
-      <c r="B22" s="215"/>
-      <c r="C22" s="215"/>
-      <c r="D22" s="216"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="207"/>
-      <c r="G22" s="145"/>
+      <c r="A22" s="207"/>
+      <c r="B22" s="208"/>
+      <c r="C22" s="208"/>
+      <c r="D22" s="209"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="210"/>
+      <c r="G22" s="142"/>
       <c r="H22" s="31"/>
-      <c r="I22" s="146"/>
-      <c r="J22" s="145"/>
+      <c r="I22" s="180"/>
+      <c r="J22" s="142"/>
       <c r="K22" s="73"/>
     </row>
     <row r="23" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="214"/>
-      <c r="B23" s="215"/>
-      <c r="C23" s="215"/>
-      <c r="D23" s="216"/>
-      <c r="E23" s="234"/>
-      <c r="F23" s="212"/>
-      <c r="G23" s="235"/>
+      <c r="A23" s="207"/>
+      <c r="B23" s="208"/>
+      <c r="C23" s="208"/>
+      <c r="D23" s="209"/>
+      <c r="E23" s="221"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="222"/>
       <c r="H23" s="24"/>
-      <c r="I23" s="234"/>
-      <c r="J23" s="235"/>
+      <c r="I23" s="221"/>
+      <c r="J23" s="222"/>
       <c r="K23" s="73"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="220" t="s">
+      <c r="A24" s="211" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="220"/>
-      <c r="C24" s="220"/>
-      <c r="D24" s="220"/>
-      <c r="E24" s="220"/>
-      <c r="F24" s="220"/>
-      <c r="G24" s="220"/>
-      <c r="H24" s="220"/>
-      <c r="I24" s="220"/>
-      <c r="J24" s="220"/>
+      <c r="B24" s="211"/>
+      <c r="C24" s="211"/>
+      <c r="D24" s="211"/>
+      <c r="E24" s="211"/>
+      <c r="F24" s="211"/>
+      <c r="G24" s="211"/>
+      <c r="H24" s="211"/>
+      <c r="I24" s="211"/>
+      <c r="J24" s="211"/>
       <c r="K24" s="84" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="221" t="s">
+      <c r="A25" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="221"/>
-      <c r="C25" s="221"/>
-      <c r="D25" s="221"/>
-      <c r="E25" s="221"/>
-      <c r="F25" s="221"/>
-      <c r="G25" s="221"/>
-      <c r="H25" s="221"/>
-      <c r="I25" s="221"/>
-      <c r="J25" s="221"/>
-      <c r="K25" s="222"/>
+      <c r="B25" s="214"/>
+      <c r="C25" s="214"/>
+      <c r="D25" s="214"/>
+      <c r="E25" s="214"/>
+      <c r="F25" s="214"/>
+      <c r="G25" s="214"/>
+      <c r="H25" s="214"/>
+      <c r="I25" s="214"/>
+      <c r="J25" s="214"/>
+      <c r="K25" s="223"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="223" t="s">
+      <c r="A26" s="194" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="224"/>
-      <c r="C26" s="224"/>
-      <c r="D26" s="225"/>
-      <c r="E26" s="228" t="s">
+      <c r="B26" s="195"/>
+      <c r="C26" s="195"/>
+      <c r="D26" s="196"/>
+      <c r="E26" s="219" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="224"/>
-      <c r="G26" s="225"/>
-      <c r="H26" s="230" t="s">
+      <c r="F26" s="195"/>
+      <c r="G26" s="196"/>
+      <c r="H26" s="200" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="228" t="s">
+      <c r="I26" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="J26" s="225"/>
-      <c r="K26" s="232" t="s">
+      <c r="J26" s="196"/>
+      <c r="K26" s="205" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="226"/>
-      <c r="B27" s="199"/>
-      <c r="C27" s="199"/>
-      <c r="D27" s="227"/>
-      <c r="E27" s="229"/>
-      <c r="F27" s="199"/>
-      <c r="G27" s="227"/>
-      <c r="H27" s="231"/>
-      <c r="I27" s="229"/>
-      <c r="J27" s="227"/>
-      <c r="K27" s="233"/>
+      <c r="A27" s="197"/>
+      <c r="B27" s="198"/>
+      <c r="C27" s="198"/>
+      <c r="D27" s="199"/>
+      <c r="E27" s="220"/>
+      <c r="F27" s="198"/>
+      <c r="G27" s="199"/>
+      <c r="H27" s="201"/>
+      <c r="I27" s="220"/>
+      <c r="J27" s="199"/>
+      <c r="K27" s="206"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="214"/>
-      <c r="B28" s="215"/>
-      <c r="C28" s="215"/>
-      <c r="D28" s="216"/>
-      <c r="E28" s="146"/>
-      <c r="F28" s="207"/>
-      <c r="G28" s="145"/>
+      <c r="A28" s="207"/>
+      <c r="B28" s="208"/>
+      <c r="C28" s="208"/>
+      <c r="D28" s="209"/>
+      <c r="E28" s="180"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="142"/>
       <c r="H28" s="61"/>
-      <c r="I28" s="146"/>
-      <c r="J28" s="145"/>
+      <c r="I28" s="180"/>
+      <c r="J28" s="142"/>
       <c r="K28" s="83" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="214"/>
-      <c r="B29" s="215"/>
-      <c r="C29" s="215"/>
-      <c r="D29" s="216"/>
-      <c r="E29" s="146"/>
-      <c r="F29" s="207"/>
-      <c r="G29" s="145"/>
+      <c r="A29" s="207"/>
+      <c r="B29" s="208"/>
+      <c r="C29" s="208"/>
+      <c r="D29" s="209"/>
+      <c r="E29" s="180"/>
+      <c r="F29" s="210"/>
+      <c r="G29" s="142"/>
       <c r="H29" s="76"/>
-      <c r="I29" s="146"/>
-      <c r="J29" s="145"/>
+      <c r="I29" s="180"/>
+      <c r="J29" s="142"/>
       <c r="K29" s="73"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="214"/>
-      <c r="B30" s="215"/>
-      <c r="C30" s="215"/>
-      <c r="D30" s="216"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="207"/>
-      <c r="G30" s="145"/>
+      <c r="A30" s="207"/>
+      <c r="B30" s="208"/>
+      <c r="C30" s="208"/>
+      <c r="D30" s="209"/>
+      <c r="E30" s="180"/>
+      <c r="F30" s="210"/>
+      <c r="G30" s="142"/>
       <c r="H30" s="75"/>
-      <c r="I30" s="146"/>
-      <c r="J30" s="145"/>
+      <c r="I30" s="180"/>
+      <c r="J30" s="142"/>
       <c r="K30" s="73"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="192" t="s">
+      <c r="A31" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="192"/>
-      <c r="C31" s="192"/>
-      <c r="D31" s="192"/>
-      <c r="E31" s="192"/>
-      <c r="F31" s="192"/>
-      <c r="G31" s="192"/>
-      <c r="H31" s="192"/>
-      <c r="I31" s="192"/>
-      <c r="J31" s="217"/>
+      <c r="B31" s="225"/>
+      <c r="C31" s="225"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="226"/>
       <c r="K31" s="84" t="s">
         <v>13</v>
       </c>
@@ -4073,49 +4070,49 @@
       <c r="K32" s="24"/>
     </row>
     <row r="33" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="218" t="s">
+      <c r="A33" s="227" t="s">
         <v>76</v>
       </c>
-      <c r="B33" s="219"/>
-      <c r="C33" s="219"/>
-      <c r="D33" s="219"/>
-      <c r="E33" s="219"/>
-      <c r="F33" s="219"/>
-      <c r="G33" s="219"/>
-      <c r="H33" s="219"/>
-      <c r="I33" s="219"/>
-      <c r="J33" s="219"/>
-      <c r="K33" s="219"/>
+      <c r="B33" s="228"/>
+      <c r="C33" s="228"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="228"/>
+      <c r="F33" s="228"/>
+      <c r="G33" s="228"/>
+      <c r="H33" s="228"/>
+      <c r="I33" s="228"/>
+      <c r="J33" s="228"/>
+      <c r="K33" s="228"/>
     </row>
     <row r="34" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="204" t="s">
+      <c r="A34" s="224" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="204"/>
-      <c r="C34" s="204"/>
-      <c r="D34" s="204"/>
-      <c r="E34" s="204"/>
-      <c r="F34" s="204"/>
-      <c r="G34" s="204"/>
-      <c r="H34" s="204"/>
-      <c r="I34" s="204"/>
-      <c r="J34" s="204"/>
-      <c r="K34" s="204"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="224"/>
+      <c r="J34" s="224"/>
+      <c r="K34" s="224"/>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="204" t="s">
+      <c r="A35" s="224" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="204"/>
-      <c r="C35" s="204"/>
-      <c r="D35" s="204"/>
-      <c r="E35" s="204"/>
-      <c r="F35" s="204"/>
-      <c r="G35" s="204"/>
-      <c r="H35" s="204"/>
-      <c r="I35" s="204"/>
-      <c r="J35" s="204"/>
-      <c r="K35" s="205"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="224"/>
+      <c r="J35" s="224"/>
+      <c r="K35" s="230"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
@@ -4123,14 +4120,14 @@
       <c r="C36" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="206"/>
-      <c r="E36" s="206"/>
-      <c r="F36" s="206"/>
-      <c r="G36" s="206"/>
-      <c r="H36" s="206"/>
+      <c r="D36" s="231"/>
+      <c r="E36" s="231"/>
+      <c r="F36" s="231"/>
+      <c r="G36" s="231"/>
+      <c r="H36" s="231"/>
       <c r="I36" s="86"/>
-      <c r="J36" s="210"/>
-      <c r="K36" s="210"/>
+      <c r="J36" s="235"/>
+      <c r="K36" s="235"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="24"/>
@@ -4139,31 +4136,31 @@
         <v>78</v>
       </c>
       <c r="D37" s="24"/>
-      <c r="E37" s="207"/>
-      <c r="F37" s="207"/>
-      <c r="G37" s="207"/>
-      <c r="H37" s="207"/>
+      <c r="E37" s="210"/>
+      <c r="F37" s="210"/>
+      <c r="G37" s="210"/>
+      <c r="H37" s="210"/>
       <c r="I37" s="77"/>
-      <c r="J37" s="211"/>
-      <c r="K37" s="211"/>
+      <c r="J37" s="236"/>
+      <c r="K37" s="236"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="24"/>
       <c r="B38" s="24"/>
-      <c r="C38" s="208" t="s">
+      <c r="C38" s="232" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="208"/>
-      <c r="E38" s="208"/>
+      <c r="D38" s="232"/>
+      <c r="E38" s="232"/>
       <c r="F38" s="24"/>
-      <c r="G38" s="207"/>
-      <c r="H38" s="207"/>
+      <c r="G38" s="210"/>
+      <c r="H38" s="210"/>
       <c r="I38" s="86"/>
-      <c r="J38" s="211" t="str">
+      <c r="J38" s="236" t="str">
         <f>IF(SUM(J36:K37)=0, "", MROUND(SUM(J36:K37), 10))</f>
         <v/>
       </c>
-      <c r="K38" s="211"/>
+      <c r="K38" s="236"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="24"/>
@@ -4187,10 +4184,10 @@
       <c r="F40" s="24"/>
       <c r="G40" s="24"/>
       <c r="H40" s="24"/>
-      <c r="I40" s="209" t="s">
+      <c r="I40" s="233" t="s">
         <v>80</v>
       </c>
-      <c r="J40" s="202"/>
+      <c r="J40" s="234"/>
       <c r="K40" s="24"/>
     </row>
     <row r="41" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4203,56 +4200,56 @@
       <c r="G41" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="H41" s="212"/>
-      <c r="I41" s="212"/>
-      <c r="J41" s="212"/>
+      <c r="H41" s="193"/>
+      <c r="I41" s="193"/>
+      <c r="J41" s="193"/>
       <c r="K41" s="24"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="213" t="s">
+      <c r="A42" s="237" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="213"/>
-      <c r="C42" s="213"/>
-      <c r="D42" s="213"/>
-      <c r="E42" s="213"/>
-      <c r="F42" s="213"/>
-      <c r="G42" s="213"/>
-      <c r="H42" s="213"/>
-      <c r="I42" s="213"/>
-      <c r="J42" s="213"/>
-      <c r="K42" s="213"/>
+      <c r="B42" s="237"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
+      <c r="I42" s="237"/>
+      <c r="J42" s="237"/>
+      <c r="K42" s="237"/>
       <c r="L42" s="24"/>
     </row>
     <row r="43" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="124" t="s">
+      <c r="A43" s="174" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="124"/>
-      <c r="C43" s="124"/>
-      <c r="D43" s="124"/>
-      <c r="E43" s="124"/>
-      <c r="F43" s="124"/>
-      <c r="G43" s="124"/>
-      <c r="H43" s="124"/>
-      <c r="I43" s="124"/>
-      <c r="J43" s="124"/>
-      <c r="K43" s="124"/>
+      <c r="B43" s="174"/>
+      <c r="C43" s="174"/>
+      <c r="D43" s="174"/>
+      <c r="E43" s="174"/>
+      <c r="F43" s="174"/>
+      <c r="G43" s="174"/>
+      <c r="H43" s="174"/>
+      <c r="I43" s="174"/>
+      <c r="J43" s="174"/>
+      <c r="K43" s="174"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="124" t="s">
+      <c r="A44" s="174" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="124"/>
-      <c r="C44" s="124"/>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-      <c r="F44" s="124"/>
-      <c r="G44" s="124"/>
-      <c r="H44" s="124"/>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
-      <c r="K44" s="124"/>
+      <c r="B44" s="174"/>
+      <c r="C44" s="174"/>
+      <c r="D44" s="174"/>
+      <c r="E44" s="174"/>
+      <c r="F44" s="174"/>
+      <c r="G44" s="174"/>
+      <c r="H44" s="174"/>
+      <c r="I44" s="174"/>
+      <c r="J44" s="174"/>
+      <c r="K44" s="174"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
@@ -4263,10 +4260,10 @@
       <c r="F45" s="24"/>
       <c r="G45" s="24"/>
       <c r="H45" s="24"/>
-      <c r="I45" s="198" t="s">
+      <c r="I45" s="238" t="s">
         <v>86</v>
       </c>
-      <c r="J45" s="198"/>
+      <c r="J45" s="238"/>
       <c r="K45" s="24"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -4277,21 +4274,21 @@
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
       <c r="G46" s="24"/>
-      <c r="H46" s="203" t="s">
+      <c r="H46" s="229" t="s">
         <v>85</v>
       </c>
-      <c r="I46" s="203"/>
-      <c r="J46" s="203"/>
-      <c r="K46" s="203"/>
+      <c r="I46" s="229"/>
+      <c r="J46" s="229"/>
+      <c r="K46" s="229"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="201" t="s">
+      <c r="A47" s="240" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="201"/>
-      <c r="C47" s="201"/>
-      <c r="D47" s="201"/>
-      <c r="E47" s="201"/>
+      <c r="B47" s="240"/>
+      <c r="C47" s="240"/>
+      <c r="D47" s="240"/>
+      <c r="E47" s="240"/>
       <c r="F47" s="24"/>
       <c r="G47" s="24"/>
       <c r="H47" s="28"/>
@@ -4300,22 +4297,22 @@
       <c r="K47" s="24"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="201" t="s">
+      <c r="A48" s="240" t="s">
         <v>89</v>
       </c>
-      <c r="B48" s="201"/>
-      <c r="C48" s="201"/>
-      <c r="D48" s="201"/>
-      <c r="E48" s="201"/>
+      <c r="B48" s="240"/>
+      <c r="C48" s="240"/>
+      <c r="D48" s="240"/>
+      <c r="E48" s="240"/>
       <c r="F48" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G48" s="24"/>
       <c r="H48" s="24"/>
-      <c r="I48" s="202" t="s">
+      <c r="I48" s="234" t="s">
         <v>90</v>
       </c>
-      <c r="J48" s="202"/>
+      <c r="J48" s="234"/>
       <c r="K48" s="24"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
@@ -4328,61 +4325,61 @@
       <c r="G49" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="H49" s="198"/>
-      <c r="I49" s="198"/>
-      <c r="J49" s="198"/>
+      <c r="H49" s="238"/>
+      <c r="I49" s="238"/>
+      <c r="J49" s="238"/>
       <c r="K49" s="24"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A50" s="124" t="s">
+      <c r="A50" s="174" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="124"/>
-      <c r="C50" s="124"/>
-      <c r="D50" s="124"/>
-      <c r="E50" s="124"/>
-      <c r="F50" s="124"/>
-      <c r="G50" s="124"/>
-      <c r="H50" s="124"/>
-      <c r="I50" s="124"/>
-      <c r="J50" s="124"/>
-      <c r="K50" s="124"/>
+      <c r="B50" s="174"/>
+      <c r="C50" s="174"/>
+      <c r="D50" s="174"/>
+      <c r="E50" s="174"/>
+      <c r="F50" s="174"/>
+      <c r="G50" s="174"/>
+      <c r="H50" s="174"/>
+      <c r="I50" s="174"/>
+      <c r="J50" s="174"/>
+      <c r="K50" s="174"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A51" s="124" t="s">
+      <c r="A51" s="174" t="s">
         <v>92</v>
       </c>
-      <c r="B51" s="124"/>
-      <c r="C51" s="124"/>
-      <c r="D51" s="124"/>
-      <c r="E51" s="124"/>
-      <c r="F51" s="124"/>
-      <c r="G51" s="124"/>
-      <c r="H51" s="124"/>
-      <c r="I51" s="124"/>
-      <c r="J51" s="124"/>
-      <c r="K51" s="124"/>
+      <c r="B51" s="174"/>
+      <c r="C51" s="174"/>
+      <c r="D51" s="174"/>
+      <c r="E51" s="174"/>
+      <c r="F51" s="174"/>
+      <c r="G51" s="174"/>
+      <c r="H51" s="174"/>
+      <c r="I51" s="174"/>
+      <c r="J51" s="174"/>
+      <c r="K51" s="174"/>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A52" s="198" t="s">
+      <c r="A52" s="238" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="198"/>
-      <c r="C52" s="198"/>
-      <c r="D52" s="198"/>
-      <c r="E52" s="198"/>
-      <c r="F52" s="198"/>
-      <c r="G52" s="198"/>
-      <c r="H52" s="198"/>
-      <c r="I52" s="198"/>
-      <c r="J52" s="198"/>
-      <c r="K52" s="198"/>
+      <c r="B52" s="238"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="238"/>
+      <c r="J52" s="238"/>
+      <c r="K52" s="238"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A53" s="199" t="s">
+      <c r="A53" s="198" t="s">
         <v>95</v>
       </c>
-      <c r="B53" s="199"/>
+      <c r="B53" s="198"/>
       <c r="C53" s="27"/>
       <c r="D53" s="27" t="s">
         <v>94</v>
@@ -4400,13 +4397,13 @@
       <c r="K53" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="M53" s="200"/>
-      <c r="N53" s="200"/>
+      <c r="M53" s="239"/>
+      <c r="N53" s="239"/>
       <c r="O53" s="24"/>
       <c r="P53" s="24"/>
       <c r="Q53" s="24"/>
-      <c r="R53" s="200"/>
-      <c r="S53" s="200"/>
+      <c r="R53" s="239"/>
+      <c r="S53" s="239"/>
       <c r="T53" s="24"/>
       <c r="U53" s="24"/>
       <c r="V53" s="24"/>
@@ -4415,8 +4412,8 @@
       <c r="Y53" s="81"/>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A54" s="143"/>
-      <c r="B54" s="143"/>
+      <c r="A54" s="178"/>
+      <c r="B54" s="178"/>
       <c r="C54" s="24"/>
       <c r="D54" s="97"/>
       <c r="E54" s="28"/>
@@ -4430,8 +4427,8 @@
       <c r="K54" s="102"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="197"/>
-      <c r="B55" s="197"/>
+      <c r="A55" s="241"/>
+      <c r="B55" s="241"/>
       <c r="C55" s="24"/>
       <c r="D55" s="101"/>
       <c r="E55" s="28"/>
@@ -4443,8 +4440,8 @@
       <c r="K55" s="102"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="197"/>
-      <c r="B56" s="197"/>
+      <c r="A56" s="241"/>
+      <c r="B56" s="241"/>
       <c r="C56" s="24"/>
       <c r="D56" s="85"/>
       <c r="E56" s="28"/>
@@ -4456,8 +4453,8 @@
       <c r="K56" s="102"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="197"/>
-      <c r="B57" s="197"/>
+      <c r="A57" s="241"/>
+      <c r="B57" s="241"/>
       <c r="C57" s="24"/>
       <c r="D57" s="85"/>
       <c r="E57" s="28"/>
@@ -4476,8 +4473,8 @@
         <f>IF(SUM(G54:G57)=0, "", MROUND(SUM(G54:G57), 10))</f>
         <v/>
       </c>
-      <c r="H58" s="124"/>
-      <c r="I58" s="124"/>
+      <c r="H58" s="174"/>
+      <c r="I58" s="174"/>
       <c r="J58" s="112" t="s">
         <v>15</v>
       </c>
@@ -4487,59 +4484,59 @@
       </c>
     </row>
     <row r="59" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="194" t="s">
+      <c r="A59" s="242" t="s">
         <v>98</v>
       </c>
-      <c r="B59" s="194"/>
-      <c r="C59" s="194"/>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="192"/>
+      <c r="B59" s="242"/>
+      <c r="C59" s="242"/>
+      <c r="D59" s="225"/>
+      <c r="E59" s="225"/>
+      <c r="F59" s="225"/>
+      <c r="G59" s="225"/>
+      <c r="H59" s="225"/>
+      <c r="I59" s="225"/>
+      <c r="J59" s="225"/>
+      <c r="K59" s="225"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A60" s="125" t="s">
+      <c r="A60" s="158" t="s">
         <v>100</v>
       </c>
-      <c r="B60" s="125"/>
-      <c r="C60" s="125"/>
-      <c r="H60" s="148" t="s">
+      <c r="B60" s="158"/>
+      <c r="C60" s="158"/>
+      <c r="H60" s="160" t="s">
         <v>99</v>
       </c>
-      <c r="I60" s="195"/>
+      <c r="I60" s="243"/>
     </row>
     <row r="61" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="196"/>
-      <c r="B61" s="196"/>
-      <c r="C61" s="196"/>
+      <c r="A61" s="244"/>
+      <c r="B61" s="244"/>
+      <c r="C61" s="244"/>
       <c r="D61" s="24"/>
       <c r="E61" s="24"/>
       <c r="F61" s="24"/>
       <c r="G61" s="24"/>
       <c r="H61" s="24"/>
-      <c r="I61" s="196"/>
-      <c r="J61" s="196"/>
+      <c r="I61" s="244"/>
+      <c r="J61" s="244"/>
       <c r="K61" s="24"/>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A62" s="190" t="s">
+      <c r="A62" s="245" t="s">
         <v>101</v>
       </c>
-      <c r="B62" s="191"/>
-      <c r="C62" s="191"/>
+      <c r="B62" s="246"/>
+      <c r="C62" s="246"/>
       <c r="D62" s="24"/>
       <c r="E62" s="24"/>
       <c r="F62" s="24"/>
       <c r="G62" s="24"/>
       <c r="H62" s="24"/>
-      <c r="I62" s="190" t="s">
+      <c r="I62" s="245" t="s">
         <v>101</v>
       </c>
-      <c r="J62" s="191"/>
+      <c r="J62" s="246"/>
       <c r="K62" s="24"/>
     </row>
     <row r="63" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4553,8 +4550,8 @@
       <c r="H63" s="113" t="s">
         <v>102</v>
       </c>
-      <c r="I63" s="192"/>
-      <c r="J63" s="192"/>
+      <c r="I63" s="225"/>
+      <c r="J63" s="225"/>
       <c r="K63" s="24"/>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
@@ -4566,10 +4563,10 @@
       <c r="F64" s="24"/>
       <c r="G64" s="24"/>
       <c r="H64" s="24"/>
-      <c r="I64" s="190" t="s">
+      <c r="I64" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="J64" s="190"/>
+      <c r="J64" s="245"/>
       <c r="K64" s="24"/>
     </row>
     <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4583,8 +4580,8 @@
       <c r="H65" s="113" t="s">
         <v>104</v>
       </c>
-      <c r="I65" s="193"/>
-      <c r="J65" s="193"/>
+      <c r="I65" s="247"/>
+      <c r="J65" s="247"/>
       <c r="K65" s="24"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4607,9 +4604,9 @@
       <c r="B67" s="24"/>
       <c r="C67" s="24"/>
       <c r="D67" s="75"/>
-      <c r="E67" s="245"/>
-      <c r="F67" s="245"/>
-      <c r="G67" s="245"/>
+      <c r="E67" s="192"/>
+      <c r="F67" s="192"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="75"/>
       <c r="I67" s="75"/>
       <c r="J67" s="114" t="s">
@@ -4621,12 +4618,12 @@
       <c r="A68" s="114" t="s">
         <v>114</v>
       </c>
-      <c r="B68" s="212"/>
-      <c r="C68" s="212"/>
-      <c r="D68" s="212"/>
-      <c r="E68" s="212"/>
-      <c r="F68" s="212"/>
-      <c r="G68" s="212"/>
+      <c r="B68" s="193"/>
+      <c r="C68" s="193"/>
+      <c r="D68" s="193"/>
+      <c r="E68" s="193"/>
+      <c r="F68" s="193"/>
+      <c r="G68" s="193"/>
       <c r="H68" s="114" t="s">
         <v>113</v>
       </c>
@@ -4643,10 +4640,10 @@
         <v>116</v>
       </c>
       <c r="D69" s="118"/>
-      <c r="E69" s="245"/>
-      <c r="F69" s="245"/>
-      <c r="G69" s="245"/>
-      <c r="H69" s="245"/>
+      <c r="E69" s="192"/>
+      <c r="F69" s="192"/>
+      <c r="G69" s="192"/>
+      <c r="H69" s="192"/>
       <c r="I69" s="24"/>
       <c r="J69" s="24"/>
       <c r="K69" s="24"/>
@@ -4666,11 +4663,94 @@
       <c r="I70" s="115" t="s">
         <v>117</v>
       </c>
-      <c r="J70" s="244"/>
-      <c r="K70" s="244"/>
+      <c r="J70" s="191"/>
+      <c r="K70" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="99">
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="D59:K59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A26:D27"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:J27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A19:D20"/>
+    <mergeCell ref="E19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="J70:K70"/>
     <mergeCell ref="E69:H69"/>
     <mergeCell ref="E67:G67"/>
@@ -4687,89 +4767,6 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A19:D20"/>
-    <mergeCell ref="E19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:J20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A26:D27"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:J27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="A50:K50"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A52:K52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="D59:K59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
